--- a/project/output/main_expt_questionnaire_results/statistical_results.xlsx
+++ b/project/output/main_expt_questionnaire_results/statistical_results.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-21 15:39:42</t>
+          <t>2026-02-03 23:48:01</t>
         </is>
       </c>
     </row>

--- a/project/output/main_expt_questionnaire_results/statistical_results.xlsx
+++ b/project/output/main_expt_questionnaire_results/statistical_results.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-03 23:48:01</t>
+          <t>2026-02-04 09:44:41</t>
         </is>
       </c>
     </row>

--- a/project/output/main_expt_questionnaire_results/statistical_results.xlsx
+++ b/project/output/main_expt_questionnaire_results/statistical_results.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-04 09:44:41</t>
+          <t>2026-02-09 18:55:38</t>
         </is>
       </c>
     </row>
